--- a/SGC-CKN/Excel/132e7f7e-d57b-4f7e-8bdc-fae6faaa6bd6_Thanh_Hoá_P1-77_D800_06-04-2026.xlsx
+++ b/SGC-CKN/Excel/132e7f7e-d57b-4f7e-8bdc-fae6faaa6bd6_Thanh_Hoá_P1-77_D800_06-04-2026.xlsx
@@ -53,13 +53,13 @@
     <t>Bắt đầu thi công</t>
   </si>
   <si>
-    <t>20:50 06/04/2026</t>
+    <t>02:50 06/04/2026</t>
   </si>
   <si>
     <t>Kết thúc thi công</t>
   </si>
   <si>
-    <t>13:53 06/04/2026</t>
+    <t>14:00 06/04/2026</t>
   </si>
   <si>
     <t>Địa chất TT</t>
@@ -112,7 +112,7 @@
     <t>2</t>
   </si>
   <si>
-    <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
+    <t>Sét lẫn hữu cơ, xám nâu, xám đen, xám trắng, xám xanh TT dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">04:30
@@ -122,7 +122,7 @@
     <t>3</t>
   </si>
   <si>
-    <t>Cát pha xám ghi, xám nâu TT dẻo</t>
+    <t>Cát pha, xám ghi, xám nâu, xám vàng, TT dẻo</t>
   </si>
   <si>
     <t xml:space="preserve">06:05
@@ -142,7 +142,7 @@
     <t>5</t>
   </si>
   <si>
-    <t>Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
+    <t>Sét xám vàng, nâu vàng, xám xanh, TT nửa cứng</t>
   </si>
   <si>
     <t xml:space="preserve">08:00
@@ -152,7 +152,7 @@
     <t>6</t>
   </si>
   <si>
-    <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
+    <t>Cát thô vừa, xám vàng, xám xanh, TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
   </si>
   <si>
     <t xml:space="preserve">09:00
@@ -162,7 +162,7 @@
     <t>7</t>
   </si>
   <si>
-    <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt chạm sỏi</t>
+    <t>Cát thô, xám vàng, xám xanh, xám nâu, KC chặt</t>
   </si>
   <si>
     <t xml:space="preserve">10:30
@@ -172,7 +172,7 @@
     <t>8</t>
   </si>
   <si>
-    <t>Sỏi xám vàng, xám xanh, TT rất chặt - Kết thúc</t>
+    <t>Sỏi xám vàng, nâu vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">14:00
@@ -1407,16 +1407,16 @@
         <v>-38.9</v>
       </c>
       <c r="G18" s="29">
-        <v>-44.3</v>
+        <v>-44.34</v>
       </c>
       <c r="H18" s="29">
         <v>3.5</v>
       </c>
       <c r="I18" s="29">
-        <v>5.4</v>
+        <v>5.44</v>
       </c>
       <c r="J18" s="12">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="K18" s="30" t="s">
         <v>30</v>
@@ -1777,16 +1777,16 @@
         <v>-38.9</v>
       </c>
       <c r="F9" s="29">
-        <v>-44.3</v>
+        <v>-44.34</v>
       </c>
       <c r="G9" s="29">
         <v>3.5</v>
       </c>
       <c r="H9" s="29">
-        <v>5.4</v>
+        <v>5.44</v>
       </c>
       <c r="I9" s="12">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1806,13 +1806,13 @@
         <v>0</v>
       </c>
       <c r="F10" s="34">
-        <v>-44.3</v>
+        <v>-44.34</v>
       </c>
       <c r="G10" s="34">
         <v>17.17</v>
       </c>
       <c r="H10" s="34">
-        <v>44.3</v>
+        <v>44.34</v>
       </c>
       <c r="I10" s="34">
         <v>2.58</v>
